--- a/dist/MWQuote/_internal/assets/TEMPLATE.xlsx
+++ b/dist/MWQuote/_internal/assets/TEMPLATE.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicolas.guinamard\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nicolas.guinamard\Documents\GitHub\MWQuote\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB384AF4-C02C-4B7D-BE06-7A90B86D01E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C130731C-40D3-4A20-80C6-2041BD809072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1230" yWindow="2670" windowWidth="21600" windowHeight="11295" tabRatio="830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="OFFRE" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">OFFRE!$A$1:$M$45</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">OFFRE!$A$1:$M$46</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="29">
   <si>
     <t xml:space="preserve">Devis N° / Quote ref : </t>
   </si>
@@ -113,7 +113,19 @@
     <t>PU_REF</t>
   </si>
   <si>
-    <t>COMMENT_REF</t>
+    <t>TOOL_REF</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>PTOOL_REF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COMMENT_REF </t>
+  </si>
+  <si>
+    <t>CUSTOMER_NAME</t>
   </si>
 </sst>
 </file>
@@ -493,26 +505,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="14" fontId="4" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -523,6 +530,12 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -538,14 +551,13 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -910,7 +922,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:P44"/>
+  <dimension ref="A2:P45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="2.140625" customWidth="1"/>
@@ -930,19 +942,19 @@
       <c r="H2" s="35" t="s">
         <v>0</v>
       </c>
-      <c r="K2" s="50" t="s">
+      <c r="K2" s="47" t="s">
         <v>18</v>
       </c>
-      <c r="L2" s="51"/>
+      <c r="L2" s="48"/>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="H3" s="35" t="s">
         <v>1</v>
       </c>
-      <c r="K3" s="57" t="s">
+      <c r="K3" s="56" t="s">
         <v>20</v>
       </c>
-      <c r="L3" s="51"/>
+      <c r="L3" s="48"/>
     </row>
     <row r="4" spans="1:16" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="M4" s="6"/>
@@ -953,17 +965,17 @@
       <c r="B6" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="44"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
+      <c r="F6" s="43"/>
       <c r="H6" s="42" t="s">
         <v>3</v>
       </c>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="44"/>
+      <c r="I6" s="41"/>
+      <c r="J6" s="41"/>
+      <c r="K6" s="41"/>
+      <c r="L6" s="43"/>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="B7" s="3"/>
@@ -976,7 +988,9 @@
         <v>4</v>
       </c>
       <c r="F8" s="7"/>
-      <c r="H8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>28</v>
+      </c>
       <c r="L8" s="7"/>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
@@ -1019,50 +1033,50 @@
         <v>5</v>
       </c>
       <c r="D14" s="11"/>
-      <c r="E14" s="54" t="s">
+      <c r="E14" s="53" t="s">
         <v>6</v>
       </c>
-      <c r="F14" s="43"/>
+      <c r="F14" s="41"/>
       <c r="G14" s="23"/>
       <c r="H14" s="11"/>
-      <c r="I14" s="49" t="s">
+      <c r="I14" s="46" t="s">
         <v>7</v>
       </c>
-      <c r="J14" s="43"/>
-      <c r="K14" s="43"/>
+      <c r="J14" s="41"/>
+      <c r="K14" s="41"/>
       <c r="L14" s="12" t="s">
         <v>8</v>
       </c>
       <c r="M14" s="9"/>
     </row>
     <row r="15" spans="1:16" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="55"/>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="45">
+      <c r="B15" s="54"/>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="60">
         <v>1000</v>
       </c>
-      <c r="F15" s="46"/>
+      <c r="F15" s="45"/>
       <c r="G15" s="24"/>
       <c r="H15" s="5"/>
-      <c r="I15" s="48" t="s">
+      <c r="I15" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J15" s="46"/>
+      <c r="J15" s="45"/>
       <c r="K15" s="5"/>
       <c r="L15" s="8"/>
     </row>
     <row r="17" spans="1:13" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="13"/>
-      <c r="B17" s="39" t="s">
+      <c r="B17" s="57" t="s">
         <v>9</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="40"/>
-      <c r="E17" s="40"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="40"/>
-      <c r="H17" s="41"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="59"/>
       <c r="I17" s="14" t="s">
         <v>10</v>
       </c>
@@ -1081,14 +1095,14 @@
       <c r="B18" s="34" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="53" t="s">
+      <c r="C18" s="52" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="43"/>
-      <c r="E18" s="43"/>
-      <c r="F18" s="43"/>
-      <c r="G18" s="43"/>
-      <c r="H18" s="44"/>
+      <c r="D18" s="41"/>
+      <c r="E18" s="41"/>
+      <c r="F18" s="41"/>
+      <c r="G18" s="41"/>
+      <c r="H18" s="43"/>
       <c r="I18" s="1"/>
       <c r="J18" s="1"/>
       <c r="K18" s="1"/>
@@ -1121,7 +1135,7 @@
       <c r="J21" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K21" s="58" t="s">
+      <c r="K21" s="39" t="s">
         <v>23</v>
       </c>
       <c r="L21" s="2" t="e">
@@ -1140,7 +1154,7 @@
       <c r="J22" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K22" s="58" t="s">
+      <c r="K22" s="39" t="s">
         <v>23</v>
       </c>
       <c r="L22" s="2" t="e">
@@ -1159,7 +1173,7 @@
       <c r="J23" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K23" s="58" t="s">
+      <c r="K23" s="39" t="s">
         <v>23</v>
       </c>
       <c r="L23" s="2" t="e">
@@ -1178,7 +1192,7 @@
       <c r="J24" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K24" s="58" t="s">
+      <c r="K24" s="39" t="s">
         <v>23</v>
       </c>
       <c r="L24" s="2" t="e">
@@ -1197,7 +1211,7 @@
       <c r="J25" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K25" s="58" t="s">
+      <c r="K25" s="39" t="s">
         <v>23</v>
       </c>
       <c r="L25" s="2" t="e">
@@ -1216,7 +1230,7 @@
       <c r="J26" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K26" s="58" t="s">
+      <c r="K26" s="39" t="s">
         <v>23</v>
       </c>
       <c r="L26" s="2" t="e">
@@ -1235,7 +1249,7 @@
       <c r="J27" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K27" s="58" t="s">
+      <c r="K27" s="39" t="s">
         <v>23</v>
       </c>
       <c r="L27" s="2" t="e">
@@ -1254,7 +1268,7 @@
       <c r="J28" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K28" s="58" t="s">
+      <c r="K28" s="39" t="s">
         <v>23</v>
       </c>
       <c r="L28" s="2" t="e">
@@ -1273,7 +1287,7 @@
       <c r="J29" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K29" s="58" t="s">
+      <c r="K29" s="39" t="s">
         <v>23</v>
       </c>
       <c r="L29" s="2" t="e">
@@ -1292,7 +1306,7 @@
       <c r="J30" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="K30" s="58" t="s">
+      <c r="K30" s="39" t="s">
         <v>23</v>
       </c>
       <c r="L30" s="2" t="e">
@@ -1379,119 +1393,138 @@
       </c>
     </row>
     <row r="37" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B37" s="36"/>
-      <c r="C37" s="37"/>
-      <c r="D37" s="37"/>
-      <c r="E37" s="37"/>
-      <c r="F37" s="37"/>
-      <c r="G37" s="37"/>
-      <c r="H37" s="38"/>
-      <c r="I37" s="25"/>
-      <c r="J37" s="25"/>
-      <c r="K37" s="26"/>
-      <c r="L37" s="27"/>
-    </row>
-    <row r="38" spans="2:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="56"/>
-      <c r="C38" s="43"/>
-      <c r="D38" s="43"/>
-      <c r="E38" s="43"/>
-      <c r="F38" s="43"/>
-      <c r="G38" s="43"/>
-      <c r="H38" s="43"/>
-      <c r="I38" s="43"/>
-      <c r="J38" s="43"/>
-      <c r="K38" s="43"/>
-      <c r="L38" s="43"/>
-    </row>
-    <row r="39" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="52" t="s">
+      <c r="B37" s="3"/>
+      <c r="H37" s="7"/>
+      <c r="I37" s="28"/>
+      <c r="J37" s="17"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="18"/>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B38" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="37"/>
+      <c r="D38" s="37"/>
+      <c r="E38" s="37"/>
+      <c r="F38" s="37"/>
+      <c r="G38" s="37"/>
+      <c r="H38" s="38"/>
+      <c r="I38" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="J38" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="K38" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="L38" s="27" t="str">
+        <f>K38</f>
+        <v>PTOOL_REF</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="55"/>
+      <c r="C39" s="41"/>
+      <c r="D39" s="41"/>
+      <c r="E39" s="41"/>
+      <c r="F39" s="41"/>
+      <c r="G39" s="41"/>
+      <c r="H39" s="41"/>
+      <c r="I39" s="41"/>
+      <c r="J39" s="41"/>
+      <c r="K39" s="41"/>
+      <c r="L39" s="41"/>
+    </row>
+    <row r="40" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="51"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="51"/>
-      <c r="K39" s="51"/>
-      <c r="L39" s="51"/>
-    </row>
-    <row r="40" spans="2:12" ht="291" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="59" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="60"/>
-      <c r="D40" s="60"/>
-      <c r="E40" s="60"/>
-      <c r="F40" s="60"/>
-      <c r="G40" s="60"/>
-      <c r="H40" s="60"/>
-      <c r="I40" s="60"/>
-      <c r="J40" s="60"/>
-      <c r="K40" s="60"/>
-      <c r="L40" s="60"/>
-    </row>
-    <row r="41" spans="2:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
-      <c r="I41" s="30"/>
-      <c r="J41" s="30"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B42" s="20"/>
-      <c r="C42" s="20"/>
-      <c r="D42" s="20"/>
-      <c r="E42" s="20"/>
-      <c r="F42" s="20"/>
-      <c r="G42" s="20"/>
-      <c r="H42" s="20"/>
-      <c r="I42" s="19"/>
-      <c r="J42" s="19"/>
-      <c r="K42" s="21"/>
-      <c r="L42" s="21"/>
-    </row>
-    <row r="44" spans="2:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="47" t="s">
+      <c r="C40" s="48"/>
+      <c r="D40" s="48"/>
+      <c r="E40" s="48"/>
+      <c r="F40" s="48"/>
+      <c r="G40" s="48"/>
+      <c r="H40" s="48"/>
+      <c r="I40" s="48"/>
+      <c r="J40" s="48"/>
+      <c r="K40" s="48"/>
+      <c r="L40" s="48"/>
+    </row>
+    <row r="41" spans="2:12" ht="291" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="50" t="s">
+        <v>27</v>
+      </c>
+      <c r="C41" s="51"/>
+      <c r="D41" s="51"/>
+      <c r="E41" s="51"/>
+      <c r="F41" s="51"/>
+      <c r="G41" s="51"/>
+      <c r="H41" s="51"/>
+      <c r="I41" s="51"/>
+      <c r="J41" s="51"/>
+      <c r="K41" s="51"/>
+      <c r="L41" s="51"/>
+    </row>
+    <row r="42" spans="2:12" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
+      <c r="D42" s="29"/>
+      <c r="E42" s="29"/>
+      <c r="F42" s="29"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="30"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="31"/>
+      <c r="L42" s="31"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B43" s="20"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="20"/>
+      <c r="E43" s="20"/>
+      <c r="F43" s="20"/>
+      <c r="G43" s="20"/>
+      <c r="H43" s="20"/>
+      <c r="I43" s="19"/>
+      <c r="J43" s="19"/>
+      <c r="K43" s="21"/>
+      <c r="L43" s="21"/>
+    </row>
+    <row r="45" spans="2:12" ht="58.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="40" t="s">
         <v>17</v>
       </c>
-      <c r="C44" s="43"/>
-      <c r="D44" s="43"/>
-      <c r="E44" s="43"/>
-      <c r="F44" s="43"/>
-      <c r="G44" s="43"/>
-      <c r="H44" s="43"/>
-      <c r="I44" s="43"/>
-      <c r="J44" s="43"/>
-      <c r="K44" s="43"/>
-      <c r="L44" s="43"/>
+      <c r="C45" s="41"/>
+      <c r="D45" s="41"/>
+      <c r="E45" s="41"/>
+      <c r="F45" s="41"/>
+      <c r="G45" s="41"/>
+      <c r="H45" s="41"/>
+      <c r="I45" s="41"/>
+      <c r="J45" s="41"/>
+      <c r="K45" s="41"/>
+      <c r="L45" s="41"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B45:L45"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="I14:K14"/>
     <mergeCell ref="K2:L2"/>
-    <mergeCell ref="B39:L39"/>
     <mergeCell ref="B40:L40"/>
+    <mergeCell ref="B41:L41"/>
     <mergeCell ref="C18:H18"/>
     <mergeCell ref="E14:F14"/>
     <mergeCell ref="B15:D15"/>
-    <mergeCell ref="B38:L38"/>
+    <mergeCell ref="B39:L39"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="B17:H17"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="E15:F15"/>
-    <mergeCell ref="B44:L44"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="I14:K14"/>
   </mergeCells>
   <printOptions horizontalCentered="1" verticalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125978" footer="0.31496062992125978"/>
